--- a/exports/trend_1d/YESBANK_full_report.xlsx
+++ b/exports/trend_1d/YESBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.94</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>166.44</v>
+        <v>161.43</v>
       </c>
       <c r="I2" t="n">
         <v>162.371323901707</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>2.34</v>
+        <v>-0.74</v>
       </c>
       <c r="L2" t="n">
         <v>1.62</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>11.85</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>164.16</v>
+        <v>176.5</v>
       </c>
       <c r="I3" t="n">
         <v>173.7113234252645</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.69</v>
+        <v>-9.34</v>
       </c>
       <c r="L3" t="n">
-        <v>4.69</v>
+        <v>10.08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.93</v>
+        <v>6.6</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>7.52</v>
       </c>
       <c r="O3" t="n">
         <v>-3.01</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.35</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>157.58</v>
+        <v>156.75</v>
       </c>
       <c r="I4" t="n">
         <v>156.7940302229822</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.72</v>
+        <v>-11.19</v>
       </c>
       <c r="L4" t="n">
-        <v>12.18</v>
+        <v>12.54</v>
       </c>
       <c r="M4" t="n">
         <v>1.37</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.91</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42143</v>
+        <v>42144</v>
       </c>
       <c r="H5" t="n">
-        <v>172.81</v>
+        <v>174.96</v>
       </c>
       <c r="I5" t="n">
         <v>173.8563598087326</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.25</v>
+        <v>-11.62</v>
       </c>
       <c r="L5" t="n">
-        <v>11.99</v>
+        <v>12.15</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42165</v>
+        <v>42166</v>
       </c>
       <c r="H6" t="n">
-        <v>166.69</v>
+        <v>160.92</v>
       </c>
       <c r="I6" t="n">
         <v>164.2704145276409</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.73</v>
+        <v>-8.02</v>
       </c>
       <c r="L6" t="n">
-        <v>6.77</v>
+        <v>8.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.48</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.79</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42186</v>
+        <v>42187</v>
       </c>
       <c r="H7" t="n">
-        <v>173.41</v>
+        <v>173.94</v>
       </c>
       <c r="I7" t="n">
         <v>173.8590800005287</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.76</v>
+        <v>-8.09</v>
       </c>
       <c r="L7" t="n">
-        <v>8.6</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>0.8</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>6.58</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42192</v>
+        <v>42193</v>
       </c>
       <c r="H8" t="n">
-        <v>172.4</v>
+        <v>159.5</v>
       </c>
       <c r="I8" t="n">
         <v>162.4884813540188</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.89</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>8.91</v>
       </c>
       <c r="M8" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="N8" t="n">
-        <v>0.87</v>
+        <v>7.48</v>
       </c>
       <c r="O8" t="n">
         <v>0.31</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42262</v>
+        <v>42263</v>
       </c>
       <c r="H9" t="n">
-        <v>145.8</v>
+        <v>151.69</v>
       </c>
       <c r="I9" t="n">
         <v>146.9705713958122</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K9" t="n">
-        <v>8.59</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>6.92</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.17</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H10" t="n">
-        <v>145.15</v>
+        <v>143.34</v>
       </c>
       <c r="I10" t="n">
         <v>144.2670124102934</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.31</v>
+        <v>-5.5</v>
       </c>
       <c r="L10" t="n">
         <v>7.34</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H11" t="n">
-        <v>134.31</v>
+        <v>149.36</v>
       </c>
       <c r="I11" t="n">
         <v>144.5954852790652</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" t="n">
-        <v>6.3</v>
+        <v>-4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>2.82</v>
+        <v>4.58</v>
       </c>
       <c r="M11" t="n">
         <v>1.94</v>
       </c>
       <c r="N11" t="n">
-        <v>4.54</v>
+        <v>11.21</v>
       </c>
       <c r="O11" t="n">
         <v>-1.25</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>18.92</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42422</v>
+        <v>42423</v>
       </c>
       <c r="H12" t="n">
-        <v>142.55</v>
+        <v>137.27</v>
       </c>
       <c r="I12" t="n">
         <v>137.3627198502178</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.56</v>
+        <v>-8.09</v>
       </c>
       <c r="L12" t="n">
         <v>12.81</v>
@@ -1125,7 +1268,7 @@
         <v>1.69</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>11.21</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>14.11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H13" t="n">
-        <v>151.91</v>
+        <v>158.12</v>
       </c>
       <c r="I13" t="n">
         <v>152.7946131717545</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.67</v>
+        <v>-15.19</v>
       </c>
       <c r="L13" t="n">
-        <v>12.12</v>
+        <v>15.6</v>
       </c>
       <c r="M13" t="n">
         <v>1.76</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.45</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42620</v>
+        <v>42621</v>
       </c>
       <c r="H14" t="n">
-        <v>280.31</v>
+        <v>265.65</v>
       </c>
       <c r="I14" t="n">
         <v>266.5554021188022</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K14" t="n">
-        <v>77.28</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>4.97</v>
@@ -1239,7 +1406,7 @@
         <v>4.37</v>
       </c>
       <c r="N14" t="n">
-        <v>4.46</v>
+        <v>5.23</v>
       </c>
       <c r="O14" t="n">
         <v>4.09</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.33</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H15" t="n">
-        <v>232.63</v>
+        <v>242.04</v>
       </c>
       <c r="I15" t="n">
         <v>238.5878881181742</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K15" t="n">
-        <v>12.43</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>4.65</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42866</v>
+        <v>42867</v>
       </c>
       <c r="H16" t="n">
-        <v>315.46</v>
+        <v>296.62</v>
       </c>
       <c r="I16" t="n">
         <v>307.9407161736972</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K16" t="n">
-        <v>30.33</v>
+        <v>22.55</v>
       </c>
       <c r="L16" t="n">
         <v>3.45</v>
@@ -1353,7 +1544,7 @@
         <v>5.29</v>
       </c>
       <c r="N16" t="n">
-        <v>3.76</v>
+        <v>5.97</v>
       </c>
       <c r="O16" t="n">
         <v>4.05</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42928</v>
+        <v>42929</v>
       </c>
       <c r="H17" t="n">
-        <v>303.09</v>
+        <v>316.4</v>
       </c>
       <c r="I17" t="n">
         <v>305.5996275712845</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.18</v>
+        <v>-6.67</v>
       </c>
       <c r="L17" t="n">
         <v>7.33</v>
@@ -1410,7 +1613,7 @@
         <v>1.37</v>
       </c>
       <c r="N17" t="n">
-        <v>2.82</v>
+        <v>4.39</v>
       </c>
       <c r="O17" t="n">
         <v>-5.97</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.31</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H18" t="n">
-        <v>360.75</v>
+        <v>353.2</v>
       </c>
       <c r="I18" t="n">
         <v>356.9170832212881</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K18" t="n">
-        <v>14.02</v>
+        <v>11.63</v>
       </c>
       <c r="L18" t="n">
         <v>4.05</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H19" t="n">
-        <v>317.1</v>
+        <v>332.85</v>
       </c>
       <c r="I19" t="n">
         <v>322.2591649999086</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>10.22</v>
+        <v>5.76</v>
       </c>
       <c r="L19" t="n">
         <v>6.43</v>
@@ -1524,7 +1751,7 @@
         <v>2.42</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>4.97</v>
       </c>
       <c r="O19" t="n">
         <v>-2.09</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.27</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43139</v>
+        <v>43140</v>
       </c>
       <c r="H20" t="n">
-        <v>335</v>
+        <v>325.55</v>
       </c>
       <c r="I20" t="n">
         <v>330.1134959887189</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>0.65</v>
+        <v>-2.19</v>
       </c>
       <c r="L20" t="n">
         <v>4.63</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.57</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43213</v>
+        <v>43214</v>
       </c>
       <c r="H21" t="n">
-        <v>313.05</v>
+        <v>324</v>
       </c>
       <c r="I21" t="n">
         <v>319.6578900615744</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K21" t="n">
-        <v>3.84</v>
+        <v>0.48</v>
       </c>
       <c r="L21" t="n">
         <v>3.78</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.41</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43341</v>
+        <v>43342</v>
       </c>
       <c r="H22" t="n">
-        <v>365.15</v>
+        <v>361.75</v>
       </c>
       <c r="I22" t="n">
         <v>363.8119120481347</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K22" t="n">
-        <v>12.7</v>
+        <v>11.65</v>
       </c>
       <c r="L22" t="n">
         <v>3.09</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43479</v>
+        <v>43480</v>
       </c>
       <c r="H23" t="n">
-        <v>195.35</v>
+        <v>203</v>
       </c>
       <c r="I23" t="n">
         <v>199.9870656728983</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K23" t="n">
-        <v>46</v>
+        <v>43.88</v>
       </c>
       <c r="L23" t="n">
         <v>2</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>13.77</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H24" t="n">
-        <v>194.1</v>
+        <v>185.6</v>
       </c>
       <c r="I24" t="n">
         <v>190.5368759836045</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.38</v>
+        <v>-8.57</v>
       </c>
       <c r="L24" t="n">
-        <v>7.68</v>
+        <v>10.71</v>
       </c>
       <c r="M24" t="n">
         <v>0.24</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>24.56</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43509</v>
+        <v>43510</v>
       </c>
       <c r="H25" t="n">
-        <v>169.45</v>
+        <v>221.25</v>
       </c>
       <c r="I25" t="n">
         <v>200.2767999677887</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>8.699999999999999</v>
+        <v>-19.21</v>
       </c>
       <c r="L25" t="n">
-        <v>6.25</v>
+        <v>20.69</v>
       </c>
       <c r="M25" t="n">
-        <v>1.59</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.28</v>
+        <v>30.57</v>
       </c>
       <c r="O25" t="n">
         <v>-4.38</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>26.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H26" t="n">
-        <v>255.8</v>
+        <v>238.35</v>
       </c>
       <c r="I26" t="n">
         <v>252.9537211340333</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K26" t="n">
-        <v>15.62</v>
+        <v>7.73</v>
       </c>
       <c r="L26" t="n">
         <v>15.77</v>
@@ -1923,7 +2234,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>6.82</v>
       </c>
       <c r="O26" t="n">
         <v>30.57</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.23</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H27" t="n">
-        <v>54.75</v>
+        <v>58.15</v>
       </c>
       <c r="I27" t="n">
         <v>56.02990499966424</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K27" t="n">
-        <v>77.03</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>6.73</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>32.09</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H28" t="n">
-        <v>62.1</v>
+        <v>56</v>
       </c>
       <c r="I28" t="n">
         <v>56.1223757377184</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K28" t="n">
-        <v>6.79</v>
+        <v>-3.7</v>
       </c>
       <c r="L28" t="n">
         <v>8.68</v>
@@ -2037,7 +2372,7 @@
         <v>9.98</v>
       </c>
       <c r="N28" t="n">
-        <v>7.1</v>
+        <v>9.82</v>
       </c>
       <c r="O28" t="n">
         <v>6.21</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>31.76</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43906</v>
+        <v>43907</v>
       </c>
       <c r="H29" t="n">
-        <v>37.1</v>
+        <v>58.65</v>
       </c>
       <c r="I29" t="n">
         <v>38.15580757604771</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K29" t="n">
-        <v>33.75</v>
+        <v>-4.73</v>
       </c>
       <c r="L29" t="n">
-        <v>8.48</v>
+        <v>15.89</v>
       </c>
       <c r="M29" t="n">
-        <v>9.880000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>45.21</v>
+        <v>58.09</v>
       </c>
       <c r="O29" t="n">
         <v>-9.82</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>59.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43914</v>
+        <v>43915</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>29.6</v>
       </c>
       <c r="I30" t="n">
         <v>31.13243763437985</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.32</v>
+        <v>-49.53</v>
       </c>
       <c r="L30" t="n">
-        <v>41.09</v>
+        <v>51.41</v>
       </c>
       <c r="M30" t="n">
         <v>9.92</v>
       </c>
       <c r="N30" t="n">
-        <v>14.86</v>
+        <v>15.43</v>
       </c>
       <c r="O30" t="n">
         <v>58.09</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>138.59</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44054</v>
+        <v>44055</v>
       </c>
       <c r="H31" t="n">
-        <v>15.5</v>
+        <v>16.25</v>
       </c>
       <c r="I31" t="n">
         <v>15.58645438058879</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K31" t="n">
-        <v>47.64</v>
+        <v>45.1</v>
       </c>
       <c r="L31" t="n">
         <v>19.93</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>6</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>17.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H32" t="n">
-        <v>13.55</v>
+        <v>13.2</v>
       </c>
       <c r="I32" t="n">
         <v>13.47751109527296</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>-16.62</v>
+        <v>-18.77</v>
       </c>
       <c r="L32" t="n">
-        <v>18.15</v>
+        <v>20.31</v>
       </c>
       <c r="M32" t="n">
         <v>2.74</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.44</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H33" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="I33" t="n">
         <v>13.23050700126875</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K33" t="n">
-        <v>2.27</v>
+        <v>-2.27</v>
       </c>
       <c r="L33" t="n">
         <v>5.68</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H34" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="I34" t="n">
         <v>17.35285136448332</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
-        <v>33.33</v>
+        <v>28.15</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>16.95</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44281</v>
+        <v>44285</v>
       </c>
       <c r="H35" t="n">
-        <v>14.05</v>
+        <v>16.3</v>
       </c>
       <c r="I35" t="n">
         <v>15.68021822446996</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K35" t="n">
-        <v>18.79</v>
+        <v>5.78</v>
       </c>
       <c r="L35" t="n">
         <v>7.51</v>
@@ -2436,7 +2855,7 @@
         <v>4.01</v>
       </c>
       <c r="N35" t="n">
-        <v>4.65</v>
+        <v>16.01</v>
       </c>
       <c r="O35" t="n">
         <v>-3.89</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>18.51</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44321</v>
+        <v>44322</v>
       </c>
       <c r="H36" t="n">
-        <v>13.85</v>
+        <v>13.55</v>
       </c>
       <c r="I36" t="n">
         <v>13.84226403172126</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.03</v>
+        <v>-16.87</v>
       </c>
       <c r="L36" t="n">
         <v>21.17</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.23</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44351</v>
+        <v>44354</v>
       </c>
       <c r="H37" t="n">
-        <v>13.75</v>
+        <v>15.05</v>
       </c>
       <c r="I37" t="n">
         <v>14.4395871606881</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.48</v>
+        <v>-11.07</v>
       </c>
       <c r="L37" t="n">
-        <v>4.06</v>
+        <v>12.18</v>
       </c>
       <c r="M37" t="n">
         <v>0.75</v>
       </c>
       <c r="N37" t="n">
-        <v>3.75</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O37" t="n">
         <v>-2.17</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.62</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44379</v>
+        <v>44382</v>
       </c>
       <c r="H38" t="n">
-        <v>13.55</v>
+        <v>13.45</v>
       </c>
       <c r="I38" t="n">
         <v>13.53583020023154</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.970000000000001</v>
+        <v>-10.63</v>
       </c>
       <c r="L38" t="n">
         <v>11.3</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44452</v>
+        <v>44453</v>
       </c>
       <c r="H39" t="n">
-        <v>11.1</v>
+        <v>12.45</v>
       </c>
       <c r="I39" t="n">
         <v>11.96832604485097</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K39" t="n">
-        <v>17.47</v>
+        <v>7.43</v>
       </c>
       <c r="L39" t="n">
         <v>4.83</v>
@@ -2664,7 +3131,7 @@
         <v>5.75</v>
       </c>
       <c r="N39" t="n">
-        <v>3.83</v>
+        <v>12.16</v>
       </c>
       <c r="O39" t="n">
         <v>-0.74</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.96</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H40" t="n">
-        <v>12.45</v>
+        <v>12.15</v>
       </c>
       <c r="I40" t="n">
         <v>12.27698258171782</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>-2.41</v>
       </c>
       <c r="L40" t="n">
         <v>11.24</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.93</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44538</v>
+        <v>44539</v>
       </c>
       <c r="H41" t="n">
-        <v>13.25</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
         <v>13.35707041434206</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.050000000000001</v>
+        <v>-15.23</v>
       </c>
       <c r="L41" t="n">
-        <v>12.76</v>
+        <v>16.87</v>
       </c>
       <c r="M41" t="n">
         <v>1.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3.97</v>
+        <v>5.66</v>
       </c>
       <c r="O41" t="n">
         <v>-2.41</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>12.55</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H42" t="n">
-        <v>13.15</v>
+        <v>12.75</v>
       </c>
       <c r="I42" t="n">
         <v>12.82064166111817</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.07</v>
+        <v>-8.93</v>
       </c>
       <c r="L42" t="n">
-        <v>6.79</v>
+        <v>10.36</v>
       </c>
       <c r="M42" t="n">
         <v>1.43</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.91</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44656</v>
+        <v>44657</v>
       </c>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="I43" t="n">
         <v>13.41731557974259</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.96</v>
+        <v>-15.29</v>
       </c>
       <c r="L43" t="n">
-        <v>17.25</v>
+        <v>19.22</v>
       </c>
       <c r="M43" t="n">
         <v>3.27</v>
       </c>
       <c r="N43" t="n">
-        <v>5</v>
+        <v>13.08</v>
       </c>
       <c r="O43" t="n">
         <v>-3.04</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>16.12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H44" t="n">
-        <v>13.75</v>
+        <v>13.55</v>
       </c>
       <c r="I44" t="n">
         <v>13.5622400733178</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.46</v>
+        <v>-7.82</v>
       </c>
       <c r="L44" t="n">
         <v>12.24</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.97</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H45" t="n">
-        <v>13.35</v>
+        <v>13.5</v>
       </c>
       <c r="I45" t="n">
         <v>13.43208965960854</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K45" t="n">
-        <v>1.48</v>
+        <v>0.37</v>
       </c>
       <c r="L45" t="n">
         <v>7.01</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.06</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H46" t="n">
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="I46" t="n">
         <v>15.80095729986856</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K46" t="n">
-        <v>20</v>
+        <v>14.81</v>
       </c>
       <c r="L46" t="n">
         <v>1.48</v>
@@ -3063,7 +3614,7 @@
         <v>2.13</v>
       </c>
       <c r="N46" t="n">
-        <v>4.08</v>
+        <v>4.32</v>
       </c>
       <c r="O46" t="n">
         <v>1.12</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>13.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44875</v>
+        <v>44876</v>
       </c>
       <c r="H47" t="n">
-        <v>16.5</v>
+        <v>16.85</v>
       </c>
       <c r="I47" t="n">
         <v>16.78315902660002</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.45</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>8.710000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="M47" t="n">
         <v>1.62</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H48" t="n">
-        <v>19.85</v>
+        <v>18.95</v>
       </c>
       <c r="I48" t="n">
         <v>19.78622710191684</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>17.8</v>
+        <v>12.46</v>
       </c>
       <c r="L48" t="n">
         <v>2.67</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>23.28</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44928</v>
+        <v>44929</v>
       </c>
       <c r="H49" t="n">
-        <v>21.65</v>
+        <v>22.05</v>
       </c>
       <c r="I49" t="n">
         <v>22.03798061651147</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.25</v>
+        <v>-16.36</v>
       </c>
       <c r="L49" t="n">
-        <v>16.62</v>
+        <v>17.41</v>
       </c>
       <c r="M49" t="n">
         <v>3.06</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>16.47</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H50" t="n">
-        <v>19.75</v>
+        <v>18.15</v>
       </c>
       <c r="I50" t="n">
         <v>18.41808470636247</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.43</v>
+        <v>-17.69</v>
       </c>
       <c r="L50" t="n">
-        <v>10.88</v>
+        <v>20.86</v>
       </c>
       <c r="M50" t="n">
-        <v>0.49</v>
+        <v>10.13</v>
       </c>
       <c r="N50" t="n">
-        <v>3.17</v>
+        <v>8.1</v>
       </c>
       <c r="O50" t="n">
         <v>1.85</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>13.64</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44985</v>
+        <v>44986</v>
       </c>
       <c r="H51" t="n">
-        <v>17.45</v>
+        <v>18.3</v>
       </c>
       <c r="I51" t="n">
         <v>17.92209290452559</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K51" t="n">
-        <v>3.86</v>
+        <v>-0.83</v>
       </c>
       <c r="L51" t="n">
         <v>2.48</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>12.7</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44995</v>
+        <v>44998</v>
       </c>
       <c r="H52" t="n">
-        <v>16.5</v>
+        <v>15.65</v>
       </c>
       <c r="I52" t="n">
         <v>15.97539293127808</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.84</v>
+        <v>-14.48</v>
       </c>
       <c r="L52" t="n">
-        <v>10.93</v>
+        <v>21.31</v>
       </c>
       <c r="M52" t="n">
-        <v>0.91</v>
+        <v>12.73</v>
       </c>
       <c r="N52" t="n">
-        <v>4.37</v>
+        <v>5.15</v>
       </c>
       <c r="O52" t="n">
         <v>4.87</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>13.68</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H53" t="n">
-        <v>15.35</v>
+        <v>16.65</v>
       </c>
       <c r="I53" t="n">
         <v>16.53589867909965</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K53" t="n">
-        <v>1.92</v>
+        <v>-6.39</v>
       </c>
       <c r="L53" t="n">
-        <v>4.15</v>
+        <v>7.35</v>
       </c>
       <c r="M53" t="n">
         <v>2.33</v>
       </c>
       <c r="N53" t="n">
-        <v>1.99</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="O53" t="n">
         <v>-5.15</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>12.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H54" t="n">
-        <v>17.3</v>
+        <v>16.35</v>
       </c>
       <c r="I54" t="n">
         <v>16.86780149308198</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K54" t="n">
-        <v>3.9</v>
+        <v>-1.8</v>
       </c>
       <c r="L54" t="n">
         <v>8.109999999999999</v>
@@ -3519,7 +4166,7 @@
         <v>4.32</v>
       </c>
       <c r="N54" t="n">
-        <v>4.62</v>
+        <v>5.49</v>
       </c>
       <c r="O54" t="n">
         <v>8.470000000000001</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>7</v>
+      </c>
+      <c r="U54" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>11.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H55" t="n">
-        <v>16.8</v>
+        <v>17.95</v>
       </c>
       <c r="I55" t="n">
         <v>17.26206349642661</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.75</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>6.73</v>
+        <v>11.93</v>
       </c>
       <c r="M55" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>2.49</v>
+        <v>6.85</v>
       </c>
       <c r="O55" t="n">
         <v>-5.49</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.67</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45342</v>
+        <v>45343</v>
       </c>
       <c r="H56" t="n">
-        <v>26.6</v>
+        <v>25.55</v>
       </c>
       <c r="I56" t="n">
         <v>25.65224621186628</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K56" t="n">
-        <v>48.19</v>
+        <v>42.34</v>
       </c>
       <c r="L56" t="n">
         <v>6.13</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>24</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45406</v>
+        <v>45407</v>
       </c>
       <c r="H57" t="n">
-        <v>25.45</v>
+        <v>25.95</v>
       </c>
       <c r="I57" t="n">
         <v>25.78159611815892</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K57" t="n">
-        <v>0.39</v>
+        <v>-1.57</v>
       </c>
       <c r="L57" t="n">
         <v>7.24</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>11.15</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H58" t="n">
-        <v>24.95</v>
+        <v>24.1</v>
       </c>
       <c r="I58" t="n">
         <v>24.66784986798416</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.85</v>
+        <v>-7.13</v>
       </c>
       <c r="L58" t="n">
-        <v>6.55</v>
+        <v>7.9</v>
       </c>
       <c r="M58" t="n">
         <v>2.36</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>15.85</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="H59" t="n">
-        <v>23.95</v>
+        <v>26.64</v>
       </c>
       <c r="I59" t="n">
         <v>24.48505815199392</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>0.62</v>
+        <v>-10.54</v>
       </c>
       <c r="L59" t="n">
-        <v>4.77</v>
+        <v>12.2</v>
       </c>
       <c r="M59" t="n">
         <v>6.09</v>
       </c>
       <c r="N59" t="n">
-        <v>3.66</v>
+        <v>11.23</v>
       </c>
       <c r="O59" t="n">
         <v>-3.41</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>14.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H60" t="n">
-        <v>25.45</v>
+        <v>23.54</v>
       </c>
       <c r="I60" t="n">
         <v>23.60036622177731</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.47</v>
+        <v>-11.64</v>
       </c>
       <c r="L60" t="n">
-        <v>10.4</v>
+        <v>12.05</v>
       </c>
       <c r="M60" t="n">
-        <v>2.21</v>
+        <v>3.73</v>
       </c>
       <c r="N60" t="n">
-        <v>3.81</v>
+        <v>7.5</v>
       </c>
       <c r="O60" t="n">
         <v>11.23</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>16.21</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H61" t="n">
-        <v>20.09</v>
+        <v>20.84</v>
       </c>
       <c r="I61" t="n">
         <v>20.81457564036985</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K61" t="n">
-        <v>14.66</v>
+        <v>11.47</v>
       </c>
       <c r="L61" t="n">
         <v>6.63</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>10.12</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H62" t="n">
-        <v>20.36</v>
+        <v>19.83</v>
       </c>
       <c r="I62" t="n">
         <v>19.99746646246104</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.3</v>
+        <v>-4.85</v>
       </c>
       <c r="L62" t="n">
-        <v>3.45</v>
+        <v>5.23</v>
       </c>
       <c r="M62" t="n">
         <v>1.55</v>
       </c>
       <c r="N62" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="O62" t="n">
         <v>3.73</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.67</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H63" t="n">
-        <v>18.95</v>
+        <v>19.23</v>
       </c>
       <c r="I63" t="n">
         <v>19.10084168090926</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K63" t="n">
-        <v>4.44</v>
+        <v>3.03</v>
       </c>
       <c r="L63" t="n">
         <v>3.38</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.29</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H64" t="n">
-        <v>18.17</v>
+        <v>17.76</v>
       </c>
       <c r="I64" t="n">
         <v>17.80925381211996</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.51</v>
+        <v>-7.64</v>
       </c>
       <c r="L64" t="n">
         <v>8.68</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.4</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="H65" t="n">
-        <v>17.4</v>
+        <v>17.95</v>
       </c>
       <c r="I65" t="n">
         <v>17.63480674173861</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K65" t="n">
-        <v>2.03</v>
+        <v>-1.07</v>
       </c>
       <c r="L65" t="n">
         <v>3.72</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>11.3</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H66" t="n">
-        <v>20.42</v>
+        <v>20.16</v>
       </c>
       <c r="I66" t="n">
         <v>20.19891589948176</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K66" t="n">
-        <v>13.76</v>
+        <v>12.31</v>
       </c>
       <c r="L66" t="n">
         <v>9.970000000000001</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.9</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H67" t="n">
-        <v>19.55</v>
+        <v>20.35</v>
       </c>
       <c r="I67" t="n">
         <v>19.76868600353794</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K67" t="n">
-        <v>3.03</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L67" t="n">
         <v>2.43</v>
@@ -4260,7 +5063,7 @@
         <v>4.77</v>
       </c>
       <c r="N67" t="n">
-        <v>2.36</v>
+        <v>4.09</v>
       </c>
       <c r="O67" t="n">
         <v>-1.27</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.77</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H68" t="n">
-        <v>23.12</v>
+        <v>22.25</v>
       </c>
       <c r="I68" t="n">
         <v>22.37466654195521</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K68" t="n">
-        <v>13.61</v>
+        <v>9.34</v>
       </c>
       <c r="L68" t="n">
         <v>3.19</v>
@@ -4317,7 +5132,7 @@
         <v>0.19</v>
       </c>
       <c r="N68" t="n">
-        <v>2.95</v>
+        <v>3.76</v>
       </c>
       <c r="O68" t="n">
         <v>4.09</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.99</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H69" t="n">
-        <v>22.29</v>
+        <v>22.83</v>
       </c>
       <c r="I69" t="n">
         <v>22.3511865604438</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.18</v>
+        <v>-2.61</v>
       </c>
       <c r="L69" t="n">
         <v>5.48</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.87</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H70" t="n">
-        <v>22.76</v>
+        <v>21.7</v>
       </c>
       <c r="I70" t="n">
         <v>21.70694990813118</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.31</v>
+        <v>-4.95</v>
       </c>
       <c r="L70" t="n">
-        <v>2.85</v>
+        <v>5.34</v>
       </c>
       <c r="M70" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="N70" t="n">
-        <v>3.32</v>
+        <v>4.66</v>
       </c>
       <c r="O70" t="n">
         <v>2.42</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>11.4</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H71" t="n">
-        <v>18.88</v>
+        <v>19.36</v>
       </c>
       <c r="I71" t="n">
         <v>19.31299935512513</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K71" t="n">
-        <v>13</v>
+        <v>10.78</v>
       </c>
       <c r="L71" t="n">
         <v>4.56</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H72" t="n">
-        <v>23.61</v>
+        <v>22.93</v>
       </c>
       <c r="I72" t="n">
         <v>23.13108108413234</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K72" t="n">
-        <v>21.95</v>
+        <v>18.44</v>
       </c>
       <c r="L72" t="n">
         <v>1.08</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>8.26</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H73" t="n">
-        <v>22.3</v>
+        <v>23.48</v>
       </c>
       <c r="I73" t="n">
         <v>23.21542652626433</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K73" t="n">
-        <v>2.75</v>
+        <v>-2.4</v>
       </c>
       <c r="L73" t="n">
-        <v>3.58</v>
+        <v>4.45</v>
       </c>
       <c r="M73" t="n">
         <v>0.44</v>
       </c>
       <c r="N73" t="n">
-        <v>3.3</v>
+        <v>5.29</v>
       </c>
       <c r="O73" t="n">
         <v>-2.88</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>8.4</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H74" t="n">
-        <v>22.5</v>
+        <v>21.18</v>
       </c>
       <c r="I74" t="n">
         <v>21.90770109419879</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.17</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>6.01</v>
+        <v>10.09</v>
       </c>
       <c r="M74" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N74" t="n">
-        <v>3.44</v>
+        <v>5.87</v>
       </c>
       <c r="O74" t="n">
         <v>5.29</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>21</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9677,7 +10584,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.1</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="6">
@@ -9687,7 +10594,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9697,7 +10604,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
@@ -9707,7 +10614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9717,7 +10624,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -9727,7 +10634,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118.8</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="11">
@@ -9737,7 +10644,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -9747,7 +10654,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -9757,7 +10664,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.6</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="14">
@@ -9767,7 +10674,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.03</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="15">
@@ -9777,7 +10684,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.52</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="16">
@@ -9787,7 +10694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.57</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="17">
@@ -9797,7 +10704,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77.28</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -9807,7 +10714,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -9817,7 +10724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.69</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="20">
@@ -9827,7 +10734,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.63</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="21">
@@ -9837,7 +10744,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>41.09</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="22">
@@ -9847,7 +10754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -9857,7 +10764,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -9867,7 +10774,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">
@@ -9877,7 +10784,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.68</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="26">
@@ -9887,7 +10794,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.99</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="27">
@@ -9897,7 +10804,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>45.21</v>
+        <v>58.09</v>
       </c>
     </row>
     <row r="28">
@@ -9907,7 +10814,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
